--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487080_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487080_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3045</v>
+        <v>3.3183</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1952</v>
+        <v>2.9949</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1092</v>
+        <v>0.3234</v>
       </c>
       <c r="G2" t="n">
         <v>2.4834</v>
@@ -610,13 +610,13 @@
         <v>0.579</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3649</v>
+        <v>0.3787</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3252</v>
+        <v>0.1249</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0396</v>
+        <v>0.2538</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1228</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.462</v>
+        <v>3.0232</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5448</v>
+        <v>3.9454</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0828</v>
+        <v>-0.9222</v>
       </c>
       <c r="G3" t="n">
         <v>-0.8667</v>
@@ -688,13 +688,13 @@
         <v>0.579</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1745</v>
+        <v>0.3867</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4019</v>
+        <v>-0.0013</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2274</v>
+        <v>0.388</v>
       </c>
       <c r="V3" t="n">
         <v>3.8892</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2653</v>
+        <v>2.0198</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3813</v>
+        <v>0.6004</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8841</v>
+        <v>1.4195</v>
       </c>
       <c r="G4" t="n">
         <v>3.9833</v>
@@ -766,13 +766,13 @@
         <v>1.9301</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5949</v>
+        <v>0.1596</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4627</v>
+        <v>-0.2435</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1322</v>
+        <v>0.4032</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. JUARROS CASTAÑO</t>
+          <t>A. BOZAL GOMEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2708</v>
+        <v>0.3262</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.1739</v>
+        <v>1.5989</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4447</v>
+        <v>-1.2727</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3165</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9055</v>
+        <v>1.4169</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5891</v>
+        <v>-2.0414</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1367</v>
+        <v>0.9831</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4502</v>
+        <v>1.6507</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5869</v>
+        <v>-0.6676</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1797</v>
+        <v>-1.6076</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3557</v>
+        <v>-0.2338</v>
       </c>
       <c r="O5" t="n">
-        <v>1.176</v>
+        <v>-1.3738</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.193</v>
+        <v>-0.579</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1231</v>
+        <v>-0.965</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9301</v>
+        <v>0.386</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0662</v>
+        <v>0.0965</v>
       </c>
       <c r="T5" t="n">
-        <v>0.08599999999999999</v>
+        <v>-0.2611</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9802</v>
+        <v>0.3576</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2859</v>
+        <v>1.4333</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.842</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2859</v>
+        <v>-0.4087</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1228</v>
+        <v>-0.2044</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4757</v>
+        <v>0.1753</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3529</v>
+        <v>-0.3797</v>
       </c>
       <c r="G6" t="n">
         <v>-0.8946</v>
@@ -922,13 +922,13 @@
         <v>0.386</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7542</v>
+        <v>0.427</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4442</v>
+        <v>0.1438</v>
       </c>
       <c r="U6" t="n">
-        <v>0.31</v>
+        <v>0.2832</v>
       </c>
       <c r="V6" t="n">
         <v>-0.1228</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ZABALETA LASA</t>
+          <t>E. JUARROS CASTAÑO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.059</v>
+        <v>-0.2378</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4382</v>
+        <v>-2.6557</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3792</v>
+        <v>2.4179</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2195</v>
+        <v>-0.3165</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2691</v>
+        <v>-0.9055</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9504</v>
+        <v>0.5891</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2611</v>
+        <v>-0.1367</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0983</v>
+        <v>0.4502</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1628</v>
+        <v>-0.5869</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4805</v>
+        <v>-0.1797</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3674</v>
+        <v>-1.3557</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1132</v>
+        <v>1.176</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.579</v>
+        <v>-0.193</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.965</v>
+        <v>-2.1231</v>
       </c>
       <c r="R7" t="n">
-        <v>0.386</v>
+        <v>1.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5341</v>
+        <v>0.5575</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2657</v>
+        <v>-0.3959</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2684</v>
+        <v>0.9534</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2053</v>
+        <v>-0.2859</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2053</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. BOZAL GOMEZ</t>
+          <t>A. ZABALETA LASA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2488</v>
+        <v>-0.5082</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3987</v>
+        <v>-0.3788</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6475</v>
+        <v>-0.1294</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6245000000000001</v>
+        <v>-1.2195</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4169</v>
+        <v>-0.2691</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0414</v>
+        <v>-0.9504</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9831</v>
+        <v>0.2611</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6507</v>
+        <v>0.0983</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6676</v>
+        <v>0.1628</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6076</v>
+        <v>-1.4805</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2338</v>
+        <v>-0.3674</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3738</v>
+        <v>-1.1132</v>
       </c>
       <c r="P8" t="n">
         <v>-0.579</v>
@@ -1078,22 +1078,22 @@
         <v>0.386</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4785</v>
+        <v>1.085</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4614</v>
+        <v>0.3252</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0172</v>
+        <v>0.7598</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4333</v>
+        <v>0.2053</v>
       </c>
       <c r="W8" t="n">
-        <v>1.842</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.4087</v>
+        <v>0.2053</v>
       </c>
     </row>
     <row r="9">
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0044</v>
+        <v>-0.7446</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9772</v>
+        <v>-0.7174</v>
       </c>
       <c r="F9" t="n">
         <v>-0.0272</v>
@@ -1156,10 +1156,10 @@
         <v>1.5441</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3556</v>
+        <v>-0.0959</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8328</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="U9" t="n">
         <v>0.4772</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0869</v>
+        <v>-1.8711</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3795</v>
+        <v>-4.3607</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2927</v>
+        <v>2.4896</v>
       </c>
       <c r="G10" t="n">
         <v>-0.1953</v>
@@ -1234,13 +1234,13 @@
         <v>2.1231</v>
       </c>
       <c r="S10" t="n">
-        <v>1.6947</v>
+        <v>0.9105</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5221</v>
+        <v>-0.5033</v>
       </c>
       <c r="U10" t="n">
-        <v>2.2169</v>
+        <v>1.4138</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6562</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4823</v>
+        <v>-1.9826</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6567</v>
+        <v>-4.2374</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1744</v>
+        <v>2.2547</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6303</v>
@@ -1312,13 +1312,13 @@
         <v>1.7371</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.466</v>
+        <v>0.0337</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1303</v>
+        <v>-0.7109</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6643</v>
+        <v>0.7446</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.544000000000001</v>
+        <v>3.1388</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.629799999999999</v>
+        <v>-3.0351</v>
       </c>
       <c r="F12" t="n">
         <v>6.1739</v>
       </c>
       <c r="G12" t="n">
-        <v>3.2359</v>
+        <v>3.235899999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8017999999999995</v>
+        <v>-0.8017999999999991</v>
       </c>
       <c r="I12" t="n">
-        <v>4.037800000000001</v>
+        <v>4.037799999999999</v>
       </c>
       <c r="J12" t="n">
         <v>11.4059</v>
@@ -1390,10 +1390,10 @@
         <v>11.5805</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3446</v>
+        <v>3.9393</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.6901</v>
+        <v>-2.0952</v>
       </c>
       <c r="U12" t="n">
         <v>6.0346</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.5156</v>
+        <v>6.7809</v>
       </c>
       <c r="E13" t="n">
-        <v>7.2681</v>
+        <v>6.6672</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2475</v>
+        <v>0.1137</v>
       </c>
       <c r="G13" t="n">
         <v>6.1016</v>
@@ -1468,13 +1468,13 @@
         <v>1.9301</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5334</v>
+        <v>-0.2013</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0925</v>
+        <v>-0.6933</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6259</v>
+        <v>0.4921</v>
       </c>
       <c r="V13" t="n">
         <v>-0.08450000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6811</v>
+        <v>2.8344</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8622</v>
+        <v>0.9623</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8189</v>
+        <v>1.8721</v>
       </c>
       <c r="G14" t="n">
         <v>0.2834</v>
@@ -1546,13 +1546,13 @@
         <v>2.8951</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8256</v>
+        <v>-0.6722</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1157</v>
+        <v>-1.0156</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2901</v>
+        <v>0.3434</v>
       </c>
       <c r="V14" t="n">
         <v>0.3281</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2537</v>
+        <v>1.9332</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1313</v>
+        <v>0.7307</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1225</v>
+        <v>1.2025</v>
       </c>
       <c r="G15" t="n">
         <v>0.3448</v>
@@ -1624,13 +1624,13 @@
         <v>1.3511</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5579</v>
+        <v>0.2373</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2062</v>
+        <v>-0.1943</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3516</v>
+        <v>0.4316</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6848</v>
+        <v>1.7711</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1306</v>
+        <v>0.431</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5542</v>
+        <v>1.3401</v>
       </c>
       <c r="G16" t="n">
         <v>0.3417</v>
@@ -1702,13 +1702,13 @@
         <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1851</v>
+        <v>0.2713</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2974</v>
+        <v>0.003</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4825</v>
+        <v>0.2683</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0177</v>
+        <v>0.1119</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2265</v>
+        <v>-0.4268</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2442</v>
+        <v>0.5386</v>
       </c>
       <c r="G17" t="n">
         <v>0.5802</v>
@@ -1780,13 +1780,13 @@
         <v>1.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5625</v>
+        <v>-0.4683</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2842</v>
+        <v>-0.4845</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2783</v>
+        <v>0.0162</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9593</v>
+        <v>-0.9725</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.4487</v>
+        <v>-2.649</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4894</v>
+        <v>1.6765</v>
       </c>
       <c r="G18" t="n">
         <v>-0.757</v>
@@ -1858,13 +1858,13 @@
         <v>1.7371</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0092</v>
+        <v>-0.0225</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2657</v>
+        <v>0.0655</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.275</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9621</v>
+        <v>-1.0424</v>
       </c>
       <c r="E19" t="n">
         <v>0.2421</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2043</v>
+        <v>-1.2846</v>
       </c>
       <c r="G19" t="n">
         <v>-1.2596</v>
@@ -1936,13 +1936,13 @@
         <v>1.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0535</v>
+        <v>-0.1338</v>
       </c>
       <c r="T19" t="n">
         <v>-0.5221</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4686</v>
+        <v>0.3883</v>
       </c>
       <c r="V19" t="n">
         <v>-0.614</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6512</v>
+        <v>-1.5976</v>
       </c>
       <c r="E20" t="n">
         <v>-0.3119</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3392</v>
+        <v>-1.2857</v>
       </c>
       <c r="G20" t="n">
         <v>-0.102</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3212</v>
+        <v>-0.2677</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3569</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0357</v>
+        <v>0.0892</v>
       </c>
       <c r="V20" t="n">
         <v>-1.228</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3375</v>
+        <v>-1.8966</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0943</v>
+        <v>-1.894</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2432</v>
+        <v>-0.0026</v>
       </c>
       <c r="G21" t="n">
         <v>-1.5585</v>
@@ -2092,13 +2092,13 @@
         <v>1.158</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6861</v>
+        <v>-0.2452</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2234</v>
+        <v>-0.0231</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4627</v>
+        <v>-0.2221</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2859</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.211</v>
+        <v>-2.5501</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.1461</v>
+        <v>-3.6454</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9350000000000001</v>
+        <v>1.0953</v>
       </c>
       <c r="G22" t="n">
         <v>-2.7807</v>
@@ -2170,13 +2170,13 @@
         <v>2.7021</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2446</v>
+        <v>-0.5836</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.7701</v>
+        <v>-1.2694</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5255</v>
+        <v>0.6857</v>
       </c>
       <c r="V22" t="n">
         <v>0.0422</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.5759</v>
+        <v>-7.2487</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.5807</v>
+        <v>-6.2803</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9952</v>
+        <v>-0.9685</v>
       </c>
       <c r="G23" t="n">
         <v>-4.4299</v>
@@ -2248,13 +2248,13 @@
         <v>2.5091</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9181</v>
+        <v>-0.5909</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.8441</v>
+        <v>-1.5437</v>
       </c>
       <c r="U23" t="n">
-        <v>0.926</v>
+        <v>0.9528</v>
       </c>
       <c r="V23" t="n">
         <v>-1.842</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.544100000000001</v>
+        <v>-1.876400000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.173899999999999</v>
+        <v>-6.174100000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>3.6298</v>
+        <v>4.297400000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-3.236</v>
@@ -2326,13 +2326,13 @@
         <v>19.3008</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.3444</v>
+        <v>-2.6769</v>
       </c>
       <c r="T24" t="n">
-        <v>-6.0345</v>
+        <v>-6.034400000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>2.689900000000001</v>
+        <v>3.3576</v>
       </c>
       <c r="V24" t="n">
         <v>-3.6841</v>
